--- a/zaini_case_audit_output/outputs/excel/04_classified_outputs.xlsx
+++ b/zaini_case_audit_output/outputs/excel/04_classified_outputs.xlsx
@@ -756,7 +756,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>حكم رقم، الدائرة</t>
+          <t>الدائرة</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="C151" s="7" t="inlineStr">
         <is>
-          <t>حكم رقم، الدائرة</t>
+          <t>الدائرة</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E151" s="7" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>حكم رقم، الدائرة</t>
+          <t>الدائرة</t>
         </is>
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="D203" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E203" s="7" t="inlineStr">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E207" s="5" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="D208" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E208" s="7" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="D209" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E209" s="6" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="D210" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E233" s="4" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="D234" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E234" s="8" t="inlineStr">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E235" s="5" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="D236" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E236" s="7" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="D237" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E237" s="6" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E269" s="3" t="inlineStr">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E270" s="4" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="D271" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E271" s="8" t="inlineStr">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="D273" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E273" s="7" t="inlineStr">
@@ -11970,7 +11970,7 @@
       </c>
       <c r="D274" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E274" s="6" t="inlineStr">
@@ -16002,7 +16002,7 @@
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="D371" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E371" s="3" t="inlineStr">
@@ -16086,7 +16086,7 @@
       </c>
       <c r="D372" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E372" s="5" t="inlineStr">
@@ -16128,7 +16128,7 @@
       </c>
       <c r="D373" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E373" s="7" t="inlineStr">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="D374" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E374" s="6" t="inlineStr">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E376" s="3" t="inlineStr">
@@ -16296,7 +16296,7 @@
       </c>
       <c r="D377" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E377" s="5" t="inlineStr">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="D378" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E378" s="7" t="inlineStr">
@@ -16380,7 +16380,7 @@
       </c>
       <c r="D379" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E379" s="6" t="inlineStr">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="D381" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E381" s="3" t="inlineStr">
@@ -16506,7 +16506,7 @@
       </c>
       <c r="D382" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E382" s="5" t="inlineStr">
@@ -16548,7 +16548,7 @@
       </c>
       <c r="D383" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E383" s="7" t="inlineStr">
@@ -16590,7 +16590,7 @@
       </c>
       <c r="D384" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E384" s="6" t="inlineStr">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="D386" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E386" s="3" t="inlineStr">
@@ -16716,7 +16716,7 @@
       </c>
       <c r="D387" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E387" s="5" t="inlineStr">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="D388" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E388" s="7" t="inlineStr">
@@ -16800,7 +16800,7 @@
       </c>
       <c r="D389" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E389" s="6" t="inlineStr">
@@ -16842,7 +16842,7 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="D391" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E391" s="3" t="inlineStr">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="D392" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E392" s="5" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="D393" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E393" s="7" t="inlineStr">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="D394" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E394" s="6" t="inlineStr">
@@ -17052,7 +17052,7 @@
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="D396" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E396" s="3" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="D397" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E397" s="5" t="inlineStr">
@@ -17178,7 +17178,7 @@
       </c>
       <c r="D398" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E398" s="7" t="inlineStr">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="D399" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E399" s="6" t="inlineStr">
@@ -17262,7 +17262,7 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="D401" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E401" s="3" t="inlineStr">
@@ -17346,7 +17346,7 @@
       </c>
       <c r="D402" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E402" s="5" t="inlineStr">
@@ -17388,7 +17388,7 @@
       </c>
       <c r="D403" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E403" s="7" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="D404" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E404" s="6" t="inlineStr">
@@ -17472,7 +17472,7 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="D406" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E406" s="3" t="inlineStr">
@@ -17556,7 +17556,7 @@
       </c>
       <c r="D407" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E407" s="5" t="inlineStr">
@@ -17598,7 +17598,7 @@
       </c>
       <c r="D408" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E408" s="7" t="inlineStr">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="D409" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E409" s="6" t="inlineStr">
@@ -17682,7 +17682,7 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="D411" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E411" s="3" t="inlineStr">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="D412" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E412" s="5" t="inlineStr">
@@ -17808,7 +17808,7 @@
       </c>
       <c r="D413" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E413" s="7" t="inlineStr">
@@ -17850,7 +17850,7 @@
       </c>
       <c r="D414" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E414" s="6" t="inlineStr">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="D416" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E416" s="3" t="inlineStr">
@@ -17976,7 +17976,7 @@
       </c>
       <c r="D417" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E417" s="5" t="inlineStr">
@@ -18018,7 +18018,7 @@
       </c>
       <c r="D418" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E418" s="7" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="D419" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E419" s="6" t="inlineStr">
@@ -18102,7 +18102,7 @@
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="D421" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E421" s="3" t="inlineStr">
@@ -18186,7 +18186,7 @@
       </c>
       <c r="D422" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E422" s="4" t="inlineStr">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="D423" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E423" s="8" t="inlineStr">
@@ -18270,7 +18270,7 @@
       </c>
       <c r="D424" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E424" s="5" t="inlineStr">
@@ -18312,7 +18312,7 @@
       </c>
       <c r="D425" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E425" s="7" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="D426" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E426" s="6" t="inlineStr">
@@ -18396,7 +18396,7 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="D428" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E428" s="3" t="inlineStr">
@@ -18480,7 +18480,7 @@
       </c>
       <c r="D429" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E429" s="4" t="inlineStr">
@@ -18522,7 +18522,7 @@
       </c>
       <c r="D430" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E430" s="8" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="D431" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E431" s="5" t="inlineStr">
@@ -18606,7 +18606,7 @@
       </c>
       <c r="D432" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E432" s="7" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="D433" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E433" s="6" t="inlineStr">
@@ -18690,7 +18690,7 @@
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
@@ -18732,7 +18732,7 @@
       </c>
       <c r="D435" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E435" s="3" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="D436" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E436" s="4" t="inlineStr">
@@ -18816,7 +18816,7 @@
       </c>
       <c r="D437" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E437" s="8" t="inlineStr">
@@ -18858,7 +18858,7 @@
       </c>
       <c r="D438" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E438" s="5" t="inlineStr">
@@ -18900,7 +18900,7 @@
       </c>
       <c r="D439" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E439" s="7" t="inlineStr">
@@ -18942,7 +18942,7 @@
       </c>
       <c r="D440" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E440" s="6" t="inlineStr">
@@ -19530,7 +19530,7 @@
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr">
@@ -19572,7 +19572,7 @@
       </c>
       <c r="D455" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E455" s="3" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="D456" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E456" s="4" t="inlineStr">
@@ -19656,7 +19656,7 @@
       </c>
       <c r="D457" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E457" s="8" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="D458" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E458" s="5" t="inlineStr">
@@ -19740,7 +19740,7 @@
       </c>
       <c r="D459" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E459" s="7" t="inlineStr">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="D460" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E460" s="6" t="inlineStr">
@@ -23142,7 +23142,7 @@
       </c>
       <c r="D540" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E540" s="2" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="D541" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E541" s="8" t="inlineStr">
@@ -23226,7 +23226,7 @@
       </c>
       <c r="D542" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E542" s="5" t="inlineStr">
@@ -23268,7 +23268,7 @@
       </c>
       <c r="D543" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E543" s="7" t="inlineStr">
@@ -23310,7 +23310,7 @@
       </c>
       <c r="D544" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E544" s="6" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="D546" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E546" s="2" t="inlineStr">
@@ -23436,7 +23436,7 @@
       </c>
       <c r="D547" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E547" s="3" t="inlineStr">
@@ -23478,7 +23478,7 @@
       </c>
       <c r="D548" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E548" s="4" t="inlineStr">
@@ -23520,7 +23520,7 @@
       </c>
       <c r="D549" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E549" s="8" t="inlineStr">
@@ -23562,7 +23562,7 @@
       </c>
       <c r="D550" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E550" s="5" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="D551" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E551" s="7" t="inlineStr">
@@ -23646,7 +23646,7 @@
       </c>
       <c r="D552" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E552" s="6" t="inlineStr">
@@ -23688,7 +23688,7 @@
       </c>
       <c r="D553" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E553" s="2" t="inlineStr">
@@ -23730,7 +23730,7 @@
       </c>
       <c r="D554" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E554" s="5" t="inlineStr">
@@ -23772,7 +23772,7 @@
       </c>
       <c r="D555" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E555" s="7" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="D556" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E556" s="6" t="inlineStr">
@@ -24738,7 +24738,7 @@
       </c>
       <c r="D578" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E578" s="3" t="inlineStr">
@@ -24775,12 +24775,12 @@
       </c>
       <c r="C579" s="7" t="inlineStr">
         <is>
-          <t>حكم رقم، الدائرة</t>
+          <t>الدائرة</t>
         </is>
       </c>
       <c r="D579" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E579" s="7" t="inlineStr">
@@ -24822,7 +24822,7 @@
       </c>
       <c r="D580" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E580" s="6" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="D581" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E581" s="3" t="inlineStr">
@@ -24901,12 +24901,12 @@
       </c>
       <c r="C582" s="7" t="inlineStr">
         <is>
-          <t>حكم رقم، الدائرة</t>
+          <t>الدائرة</t>
         </is>
       </c>
       <c r="D582" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E582" s="7" t="inlineStr">
@@ -24948,7 +24948,7 @@
       </c>
       <c r="D583" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E583" s="6" t="inlineStr">
@@ -24990,7 +24990,7 @@
       </c>
       <c r="D584" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E584" s="2" t="inlineStr">
@@ -25032,7 +25032,7 @@
       </c>
       <c r="D585" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E585" s="8" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="D586" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E586" s="5" t="inlineStr">
@@ -25116,7 +25116,7 @@
       </c>
       <c r="D587" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E587" s="7" t="inlineStr">
@@ -25158,7 +25158,7 @@
       </c>
       <c r="D588" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E588" s="6" t="inlineStr">
@@ -25200,7 +25200,7 @@
       </c>
       <c r="D589" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E589" s="2" t="inlineStr">
@@ -25242,7 +25242,7 @@
       </c>
       <c r="D590" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E590" s="3" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="D591" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E591" s="4" t="inlineStr">
@@ -25326,7 +25326,7 @@
       </c>
       <c r="D592" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E592" s="8" t="inlineStr">
@@ -25368,7 +25368,7 @@
       </c>
       <c r="D593" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E593" s="5" t="inlineStr">
@@ -25410,7 +25410,7 @@
       </c>
       <c r="D594" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E594" s="7" t="inlineStr">
@@ -25452,7 +25452,7 @@
       </c>
       <c r="D595" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E595" s="6" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="D596" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E596" s="2" t="inlineStr">
@@ -25536,7 +25536,7 @@
       </c>
       <c r="D597" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E597" s="3" t="inlineStr">
@@ -25578,7 +25578,7 @@
       </c>
       <c r="D598" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E598" s="4" t="inlineStr">
@@ -25620,7 +25620,7 @@
       </c>
       <c r="D599" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E599" s="8" t="inlineStr">
@@ -25662,7 +25662,7 @@
       </c>
       <c r="D600" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E600" s="5" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="D601" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E601" s="7" t="inlineStr">
@@ -25746,7 +25746,7 @@
       </c>
       <c r="D602" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E602" s="6" t="inlineStr">
@@ -26082,7 +26082,7 @@
       </c>
       <c r="D610" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E610" s="2" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="D611" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E611" s="3" t="inlineStr">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="D612" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E612" s="4" t="inlineStr">
@@ -26208,7 +26208,7 @@
       </c>
       <c r="D613" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E613" s="8" t="inlineStr">
@@ -26250,7 +26250,7 @@
       </c>
       <c r="D614" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E614" s="5" t="inlineStr">
@@ -26292,7 +26292,7 @@
       </c>
       <c r="D615" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E615" s="7" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="D616" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E616" s="6" t="inlineStr">
@@ -26376,7 +26376,7 @@
       </c>
       <c r="D617" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E617" s="2" t="inlineStr">
@@ -26418,7 +26418,7 @@
       </c>
       <c r="D618" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E618" s="3" t="inlineStr">
@@ -26460,7 +26460,7 @@
       </c>
       <c r="D619" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E619" s="4" t="inlineStr">
@@ -26502,7 +26502,7 @@
       </c>
       <c r="D620" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E620" s="8" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="D621" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E621" s="5" t="inlineStr">
@@ -26586,7 +26586,7 @@
       </c>
       <c r="D622" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E622" s="7" t="inlineStr">
@@ -26628,7 +26628,7 @@
       </c>
       <c r="D623" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E623" s="6" t="inlineStr">
@@ -27552,7 +27552,7 @@
       </c>
       <c r="D645" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E645" s="2" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="D646" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E646" s="3" t="inlineStr">
@@ -27636,7 +27636,7 @@
       </c>
       <c r="D647" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E647" s="4" t="inlineStr">
@@ -27678,7 +27678,7 @@
       </c>
       <c r="D648" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E648" s="8" t="inlineStr">
@@ -27720,7 +27720,7 @@
       </c>
       <c r="D649" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E649" s="5" t="inlineStr">
@@ -27762,7 +27762,7 @@
       </c>
       <c r="D650" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E650" s="7" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="D651" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E651" s="6" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="D666" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E666" s="2" t="inlineStr">
@@ -28476,7 +28476,7 @@
       </c>
       <c r="D667" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E667" s="3" t="inlineStr">
@@ -28518,7 +28518,7 @@
       </c>
       <c r="D668" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E668" s="4" t="inlineStr">
@@ -28560,7 +28560,7 @@
       </c>
       <c r="D669" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E669" s="8" t="inlineStr">
@@ -28602,7 +28602,7 @@
       </c>
       <c r="D670" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E670" s="5" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="D671" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E671" s="7" t="inlineStr">
@@ -28686,7 +28686,7 @@
       </c>
       <c r="D672" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E672" s="6" t="inlineStr">
@@ -28728,7 +28728,7 @@
       </c>
       <c r="D673" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E673" s="2" t="inlineStr">
@@ -28770,7 +28770,7 @@
       </c>
       <c r="D674" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E674" s="3" t="inlineStr">
@@ -28812,7 +28812,7 @@
       </c>
       <c r="D675" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E675" s="4" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="D676" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E676" s="8" t="inlineStr">
@@ -28896,7 +28896,7 @@
       </c>
       <c r="D677" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E677" s="5" t="inlineStr">
@@ -28938,7 +28938,7 @@
       </c>
       <c r="D678" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E678" s="7" t="inlineStr">
@@ -28980,7 +28980,7 @@
       </c>
       <c r="D679" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E679" s="6" t="inlineStr">
@@ -29568,7 +29568,7 @@
       </c>
       <c r="D693" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E693" s="2" t="inlineStr">
@@ -29610,7 +29610,7 @@
       </c>
       <c r="D694" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E694" s="4" t="inlineStr">
@@ -29652,7 +29652,7 @@
       </c>
       <c r="D695" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E695" s="5" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="D696" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E696" s="7" t="inlineStr">
@@ -29736,7 +29736,7 @@
       </c>
       <c r="D697" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E697" s="6" t="inlineStr">
@@ -29778,7 +29778,7 @@
       </c>
       <c r="D698" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E698" s="2" t="inlineStr">
@@ -29820,7 +29820,7 @@
       </c>
       <c r="D699" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E699" s="3" t="inlineStr">
@@ -29862,7 +29862,7 @@
       </c>
       <c r="D700" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E700" s="4" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="D701" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E701" s="8" t="inlineStr">
@@ -29946,7 +29946,7 @@
       </c>
       <c r="D702" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E702" s="5" t="inlineStr">
@@ -29983,12 +29983,12 @@
       </c>
       <c r="C703" s="7" t="inlineStr">
         <is>
-          <t>حكم رقم، صك رقم، الدائرة، الاستئناف، المبدأ القضائي</t>
+          <t>صك رقم، الدائرة، الاستئناف، المبدأ القضائي</t>
         </is>
       </c>
       <c r="D703" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E703" s="7" t="inlineStr">
@@ -30030,7 +30030,7 @@
       </c>
       <c r="D704" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E704" s="6" t="inlineStr">
@@ -30366,7 +30366,7 @@
       </c>
       <c r="D712" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E712" s="5" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="D721" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E721" s="2" t="inlineStr">
@@ -30786,7 +30786,7 @@
       </c>
       <c r="D722" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E722" s="3" t="inlineStr">
@@ -30828,7 +30828,7 @@
       </c>
       <c r="D723" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E723" s="4" t="inlineStr">
@@ -30870,7 +30870,7 @@
       </c>
       <c r="D724" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E724" s="8" t="inlineStr">
@@ -30912,7 +30912,7 @@
       </c>
       <c r="D725" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E725" s="5" t="inlineStr">
@@ -30949,12 +30949,12 @@
       </c>
       <c r="C726" s="7" t="inlineStr">
         <is>
-          <t>حكم رقم، صك رقم، الدائرة، الاستئناف، المبدأ القضائي</t>
+          <t>صك رقم، الدائرة، الاستئناف، المبدأ القضائي</t>
         </is>
       </c>
       <c r="D726" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E726" s="7" t="inlineStr">
@@ -30996,7 +30996,7 @@
       </c>
       <c r="D727" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E727" s="6" t="inlineStr">
@@ -31038,7 +31038,7 @@
       </c>
       <c r="D728" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E728" s="2" t="inlineStr">
@@ -31080,7 +31080,7 @@
       </c>
       <c r="D729" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E729" s="3" t="inlineStr">
@@ -31122,7 +31122,7 @@
       </c>
       <c r="D730" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E730" s="4" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="D731" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E731" s="8" t="inlineStr">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="D732" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E732" s="5" t="inlineStr">
@@ -31248,7 +31248,7 @@
       </c>
       <c r="D733" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E733" s="7" t="inlineStr">
@@ -31290,7 +31290,7 @@
       </c>
       <c r="D734" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E734" s="6" t="inlineStr">
@@ -31332,7 +31332,7 @@
       </c>
       <c r="D735" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E735" s="2" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="D736" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E736" s="3" t="inlineStr">
@@ -31416,7 +31416,7 @@
       </c>
       <c r="D737" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E737" s="4" t="inlineStr">
@@ -31458,7 +31458,7 @@
       </c>
       <c r="D738" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E738" s="8" t="inlineStr">
@@ -31500,7 +31500,7 @@
       </c>
       <c r="D739" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E739" s="5" t="inlineStr">
@@ -31542,7 +31542,7 @@
       </c>
       <c r="D740" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E740" s="7" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="D741" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E741" s="6" t="inlineStr">
@@ -31626,7 +31626,7 @@
       </c>
       <c r="D742" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E742" s="2" t="inlineStr">
@@ -31668,7 +31668,7 @@
       </c>
       <c r="D743" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E743" s="8" t="inlineStr">
@@ -31710,7 +31710,7 @@
       </c>
       <c r="D744" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E744" s="5" t="inlineStr">
@@ -31752,7 +31752,7 @@
       </c>
       <c r="D745" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E745" s="7" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="D746" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E746" s="6" t="inlineStr">
@@ -31836,7 +31836,7 @@
       </c>
       <c r="D747" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E747" s="2" t="inlineStr">
@@ -31878,7 +31878,7 @@
       </c>
       <c r="D748" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E748" s="3" t="inlineStr">
@@ -31920,7 +31920,7 @@
       </c>
       <c r="D749" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E749" s="4" t="inlineStr">
@@ -31962,7 +31962,7 @@
       </c>
       <c r="D750" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E750" s="8" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="D751" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E751" s="5" t="inlineStr">
@@ -32046,7 +32046,7 @@
       </c>
       <c r="D752" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E752" s="7" t="inlineStr">
@@ -32088,7 +32088,7 @@
       </c>
       <c r="D753" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E753" s="6" t="inlineStr">
@@ -32466,7 +32466,7 @@
       </c>
       <c r="D762" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E762" s="2" t="inlineStr">
@@ -32508,7 +32508,7 @@
       </c>
       <c r="D763" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E763" s="3" t="inlineStr">
@@ -32550,7 +32550,7 @@
       </c>
       <c r="D764" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E764" s="4" t="inlineStr">
@@ -32592,7 +32592,7 @@
       </c>
       <c r="D765" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E765" s="8" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="D766" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E766" s="5" t="inlineStr">
@@ -32676,7 +32676,7 @@
       </c>
       <c r="D767" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E767" s="7" t="inlineStr">
@@ -32718,7 +32718,7 @@
       </c>
       <c r="D768" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E768" s="6" t="inlineStr">
@@ -32760,7 +32760,7 @@
       </c>
       <c r="D769" s="2" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E769" s="2" t="inlineStr">
@@ -32802,7 +32802,7 @@
       </c>
       <c r="D770" s="3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E770" s="3" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="D771" s="4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E771" s="4" t="inlineStr">
@@ -32886,7 +32886,7 @@
       </c>
       <c r="D772" s="8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E772" s="8" t="inlineStr">
@@ -32928,7 +32928,7 @@
       </c>
       <c r="D773" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E773" s="5" t="inlineStr">
@@ -32965,12 +32965,12 @@
       </c>
       <c r="C774" s="7" t="inlineStr">
         <is>
-          <t>حكم رقم، صك رقم، الدائرة، الاستئناف</t>
+          <t>صك رقم، الدائرة، الاستئناف</t>
         </is>
       </c>
       <c r="D774" s="7" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E774" s="7" t="inlineStr">
@@ -33012,7 +33012,7 @@
       </c>
       <c r="D775" s="6" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E775" s="6" t="inlineStr">
@@ -33348,7 +33348,7 @@
       </c>
       <c r="D783" s="5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="E783" s="5" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/04_classified_outputs.xlsx
+++ b/zaini_case_audit_output/outputs/excel/04_classified_outputs.xlsx
@@ -2389,7 +2389,7 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>الدائرة</t>
+          <t>حكم رقم، الدائرة</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="C151" s="7" t="inlineStr">
         <is>
-          <t>الدائرة</t>
+          <t>حكم رقم، الدائرة</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>الدائرة</t>
+          <t>حكم رقم، الدائرة</t>
         </is>
       </c>
       <c r="D154" s="7" t="inlineStr">
@@ -24775,7 +24775,7 @@
       </c>
       <c r="C579" s="7" t="inlineStr">
         <is>
-          <t>الدائرة</t>
+          <t>حكم رقم، الدائرة</t>
         </is>
       </c>
       <c r="D579" s="7" t="inlineStr">
@@ -24901,7 +24901,7 @@
       </c>
       <c r="C582" s="7" t="inlineStr">
         <is>
-          <t>الدائرة</t>
+          <t>حكم رقم، الدائرة</t>
         </is>
       </c>
       <c r="D582" s="7" t="inlineStr">
@@ -29983,7 +29983,7 @@
       </c>
       <c r="C703" s="7" t="inlineStr">
         <is>
-          <t>صك رقم، الدائرة، الاستئناف، المبدأ القضائي</t>
+          <t>حكم رقم، صك رقم، الدائرة، الاستئناف، المبدأ القضائي</t>
         </is>
       </c>
       <c r="D703" s="7" t="inlineStr">
@@ -30949,7 +30949,7 @@
       </c>
       <c r="C726" s="7" t="inlineStr">
         <is>
-          <t>صك رقم، الدائرة، الاستئناف، المبدأ القضائي</t>
+          <t>حكم رقم، صك رقم، الدائرة، الاستئناف، المبدأ القضائي</t>
         </is>
       </c>
       <c r="D726" s="7" t="inlineStr">
@@ -32965,7 +32965,7 @@
       </c>
       <c r="C774" s="7" t="inlineStr">
         <is>
-          <t>صك رقم، الدائرة، الاستئناف</t>
+          <t>حكم رقم، صك رقم، الدائرة، الاستئناف</t>
         </is>
       </c>
       <c r="D774" s="7" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/04_classified_outputs.xlsx
+++ b/zaini_case_audit_output/outputs/excel/04_classified_outputs.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H794"/>
+  <dimension ref="A1:H811"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -33834,6 +33834,652 @@
         </is>
       </c>
     </row>
+    <row r="795">
+      <c r="A795" s="2" t="inlineStr">
+        <is>
+          <t>مستند_جديد_1_14041442.pdf</t>
+        </is>
+      </c>
+      <c r="B795" s="2" t="inlineStr">
+        <is>
+          <t>واقعة قانونية</t>
+        </is>
+      </c>
+      <c r="C795" s="2" t="inlineStr">
+        <is>
+          <t>بتاريخ، تقدم، توفي، اشترى، باع، وقع، ابرم، أبرم</t>
+        </is>
+      </c>
+      <c r="D795" s="2" t="inlineStr">
+        <is>
+          <t>logical</t>
+        </is>
+      </c>
+      <c r="E795" s="2" t="inlineStr"/>
+      <c r="F795" s="2" t="inlineStr">
+        <is>
+          <t>واقعة قانونية</t>
+        </is>
+      </c>
+      <c r="G795" s="2" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H795" s="2" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="3" t="inlineStr">
+        <is>
+          <t>مستند_جديد_1_14041442.pdf</t>
+        </is>
+      </c>
+      <c r="B796" s="3" t="inlineStr">
+        <is>
+          <t>نتيجة قانونية</t>
+        </is>
+      </c>
+      <c r="C796" s="3" t="inlineStr">
+        <is>
+          <t>حكمت، تقرر، قضت، قبول، الزام، إلزام، بطلان</t>
+        </is>
+      </c>
+      <c r="D796" s="3" t="inlineStr">
+        <is>
+          <t>logical</t>
+        </is>
+      </c>
+      <c r="E796" s="3" t="inlineStr"/>
+      <c r="F796" s="3" t="inlineStr">
+        <is>
+          <t>نتيجة قانونية</t>
+        </is>
+      </c>
+      <c r="G796" s="3" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H796" s="3" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="4" t="inlineStr">
+        <is>
+          <t>مستند_جديد_1_14041442.pdf</t>
+        </is>
+      </c>
+      <c r="B797" s="4" t="inlineStr">
+        <is>
+          <t>دفع قانوني</t>
+        </is>
+      </c>
+      <c r="C797" s="4" t="inlineStr">
+        <is>
+          <t>دفع، الدفع، استدلال، نتمسك، الدفوع</t>
+        </is>
+      </c>
+      <c r="D797" s="4" t="inlineStr">
+        <is>
+          <t>logical</t>
+        </is>
+      </c>
+      <c r="E797" s="4" t="inlineStr"/>
+      <c r="F797" s="4" t="inlineStr">
+        <is>
+          <t>دفع قانوني</t>
+        </is>
+      </c>
+      <c r="G797" s="4" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H797" s="4" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="7" t="inlineStr">
+        <is>
+          <t>مستند_جديد_1_14041442.pdf</t>
+        </is>
+      </c>
+      <c r="B798" s="7" t="inlineStr">
+        <is>
+          <t>مخاطر/إشكال/تعارض</t>
+        </is>
+      </c>
+      <c r="C798" s="7" t="inlineStr">
+        <is>
+          <t>تعارض، تناقض، نقص</t>
+        </is>
+      </c>
+      <c r="D798" s="7" t="inlineStr">
+        <is>
+          <t>logical</t>
+        </is>
+      </c>
+      <c r="E798" s="7" t="inlineStr"/>
+      <c r="F798" s="7" t="inlineStr">
+        <is>
+          <t>مخاطر/إشكال/تعارض</t>
+        </is>
+      </c>
+      <c r="G798" s="7" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H798" s="7" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="5" t="inlineStr">
+        <is>
+          <t>مستند_جديد_1_14041442.pdf</t>
+        </is>
+      </c>
+      <c r="B799" s="5" t="inlineStr">
+        <is>
+          <t>إحالة نظامية</t>
+        </is>
+      </c>
+      <c r="C799" s="5" t="inlineStr">
+        <is>
+          <t>نظام، المادة، اللائحة، اللائحه، النظام</t>
+        </is>
+      </c>
+      <c r="D799" s="5" t="inlineStr">
+        <is>
+          <t>logical</t>
+        </is>
+      </c>
+      <c r="E799" s="5" t="inlineStr"/>
+      <c r="F799" s="5" t="inlineStr">
+        <is>
+          <t>إحالة نظامية</t>
+        </is>
+      </c>
+      <c r="G799" s="5" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H799" s="5" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="8" t="inlineStr">
+        <is>
+          <t>مستند_جديد_1_14041442.pdf</t>
+        </is>
+      </c>
+      <c r="B800" s="8" t="inlineStr">
+        <is>
+          <t>إحالة قضائية</t>
+        </is>
+      </c>
+      <c r="C800" s="8" t="inlineStr">
+        <is>
+          <t>صك رقم، الدائرة، الاستئناف</t>
+        </is>
+      </c>
+      <c r="D800" s="8" t="inlineStr">
+        <is>
+          <t>logical</t>
+        </is>
+      </c>
+      <c r="E800" s="8" t="inlineStr"/>
+      <c r="F800" s="8" t="inlineStr">
+        <is>
+          <t>إحالة قضائية</t>
+        </is>
+      </c>
+      <c r="G800" s="8" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H800" s="8" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="6" t="inlineStr">
+        <is>
+          <t>مستند_جديد_1_14041442.pdf</t>
+        </is>
+      </c>
+      <c r="B801" s="6" t="inlineStr">
+        <is>
+          <t>دليل/مستند</t>
+        </is>
+      </c>
+      <c r="C801" s="6" t="inlineStr">
+        <is>
+          <t>مرفق، مستند، صورة، نسخة، بموجب، سند</t>
+        </is>
+      </c>
+      <c r="D801" s="6" t="inlineStr">
+        <is>
+          <t>logical</t>
+        </is>
+      </c>
+      <c r="E801" s="6" t="inlineStr"/>
+      <c r="F801" s="6" t="inlineStr">
+        <is>
+          <t>دليل/مستند</t>
+        </is>
+      </c>
+      <c r="G801" s="6" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H801" s="6" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="2" t="inlineStr">
+        <is>
+          <t>مستند_جديد_2_427036.pdf</t>
+        </is>
+      </c>
+      <c r="B802" s="2" t="inlineStr">
+        <is>
+          <t>واقعة قانونية</t>
+        </is>
+      </c>
+      <c r="C802" s="2" t="inlineStr">
+        <is>
+          <t>تقدم، توفي، الورثة</t>
+        </is>
+      </c>
+      <c r="D802" s="2" t="inlineStr">
+        <is>
+          <t>logical</t>
+        </is>
+      </c>
+      <c r="E802" s="2" t="inlineStr"/>
+      <c r="F802" s="2" t="inlineStr">
+        <is>
+          <t>واقعة قانونية</t>
+        </is>
+      </c>
+      <c r="G802" s="2" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H802" s="2" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="3" t="inlineStr">
+        <is>
+          <t>مستند_جديد_2_427036.pdf</t>
+        </is>
+      </c>
+      <c r="B803" s="3" t="inlineStr">
+        <is>
+          <t>نتيجة قانونية</t>
+        </is>
+      </c>
+      <c r="C803" s="3" t="inlineStr">
+        <is>
+          <t>حكمت، تقرر، رفض، قبول، الزام، إلزام، رد الدعوى</t>
+        </is>
+      </c>
+      <c r="D803" s="3" t="inlineStr">
+        <is>
+          <t>logical</t>
+        </is>
+      </c>
+      <c r="E803" s="3" t="inlineStr"/>
+      <c r="F803" s="3" t="inlineStr">
+        <is>
+          <t>نتيجة قانونية</t>
+        </is>
+      </c>
+      <c r="G803" s="3" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H803" s="3" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="7" t="inlineStr">
+        <is>
+          <t>مستند_جديد_2_427036.pdf</t>
+        </is>
+      </c>
+      <c r="B804" s="7" t="inlineStr">
+        <is>
+          <t>مخاطر/إشكال/تعارض</t>
+        </is>
+      </c>
+      <c r="C804" s="7" t="inlineStr">
+        <is>
+          <t>تعارض، تناقض</t>
+        </is>
+      </c>
+      <c r="D804" s="7" t="inlineStr">
+        <is>
+          <t>logical</t>
+        </is>
+      </c>
+      <c r="E804" s="7" t="inlineStr"/>
+      <c r="F804" s="7" t="inlineStr">
+        <is>
+          <t>مخاطر/إشكال/تعارض</t>
+        </is>
+      </c>
+      <c r="G804" s="7" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H804" s="7" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="5" t="inlineStr">
+        <is>
+          <t>مستند_جديد_2_427036.pdf</t>
+        </is>
+      </c>
+      <c r="B805" s="5" t="inlineStr">
+        <is>
+          <t>إحالة نظامية</t>
+        </is>
+      </c>
+      <c r="C805" s="5" t="inlineStr">
+        <is>
+          <t>نظام، النظام</t>
+        </is>
+      </c>
+      <c r="D805" s="5" t="inlineStr">
+        <is>
+          <t>logical</t>
+        </is>
+      </c>
+      <c r="E805" s="5" t="inlineStr"/>
+      <c r="F805" s="5" t="inlineStr">
+        <is>
+          <t>إحالة نظامية</t>
+        </is>
+      </c>
+      <c r="G805" s="5" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H805" s="5" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="8" t="inlineStr">
+        <is>
+          <t>مستند_جديد_2_427036.pdf</t>
+        </is>
+      </c>
+      <c r="B806" s="8" t="inlineStr">
+        <is>
+          <t>إحالة قضائية</t>
+        </is>
+      </c>
+      <c r="C806" s="8" t="inlineStr">
+        <is>
+          <t>صك رقم، الدائرة</t>
+        </is>
+      </c>
+      <c r="D806" s="8" t="inlineStr">
+        <is>
+          <t>logical</t>
+        </is>
+      </c>
+      <c r="E806" s="8" t="inlineStr"/>
+      <c r="F806" s="8" t="inlineStr">
+        <is>
+          <t>إحالة قضائية</t>
+        </is>
+      </c>
+      <c r="G806" s="8" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H806" s="8" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="6" t="inlineStr">
+        <is>
+          <t>مستند_جديد_2_427036.pdf</t>
+        </is>
+      </c>
+      <c r="B807" s="6" t="inlineStr">
+        <is>
+          <t>دليل/مستند</t>
+        </is>
+      </c>
+      <c r="C807" s="6" t="inlineStr">
+        <is>
+          <t>بموجب، سند</t>
+        </is>
+      </c>
+      <c r="D807" s="6" t="inlineStr">
+        <is>
+          <t>logical</t>
+        </is>
+      </c>
+      <c r="E807" s="6" t="inlineStr"/>
+      <c r="F807" s="6" t="inlineStr">
+        <is>
+          <t>دليل/مستند</t>
+        </is>
+      </c>
+      <c r="G807" s="6" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H807" s="6" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="2" t="inlineStr">
+        <is>
+          <t>مستند_جديد_3_18121427.pdf</t>
+        </is>
+      </c>
+      <c r="B808" s="2" t="inlineStr">
+        <is>
+          <t>واقعة قانونية</t>
+        </is>
+      </c>
+      <c r="C808" s="2" t="inlineStr">
+        <is>
+          <t>بتاريخ، توفي، وقع، حرر، استلم، الورثة</t>
+        </is>
+      </c>
+      <c r="D808" s="2" t="inlineStr">
+        <is>
+          <t>logical</t>
+        </is>
+      </c>
+      <c r="E808" s="2" t="inlineStr"/>
+      <c r="F808" s="2" t="inlineStr">
+        <is>
+          <t>واقعة قانونية</t>
+        </is>
+      </c>
+      <c r="G808" s="2" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H808" s="2" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="3" t="inlineStr">
+        <is>
+          <t>مستند_جديد_3_18121427.pdf</t>
+        </is>
+      </c>
+      <c r="B809" s="3" t="inlineStr">
+        <is>
+          <t>نتيجة قانونية</t>
+        </is>
+      </c>
+      <c r="C809" s="3" t="inlineStr">
+        <is>
+          <t>ثبت لدى، قبول</t>
+        </is>
+      </c>
+      <c r="D809" s="3" t="inlineStr">
+        <is>
+          <t>logical</t>
+        </is>
+      </c>
+      <c r="E809" s="3" t="inlineStr"/>
+      <c r="F809" s="3" t="inlineStr">
+        <is>
+          <t>نتيجة قانونية</t>
+        </is>
+      </c>
+      <c r="G809" s="3" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H809" s="3" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="5" t="inlineStr">
+        <is>
+          <t>مستند_جديد_3_18121427.pdf</t>
+        </is>
+      </c>
+      <c r="B810" s="5" t="inlineStr">
+        <is>
+          <t>إحالة نظامية</t>
+        </is>
+      </c>
+      <c r="C810" s="5" t="inlineStr">
+        <is>
+          <t>نظام، المادة، النظام</t>
+        </is>
+      </c>
+      <c r="D810" s="5" t="inlineStr">
+        <is>
+          <t>logical</t>
+        </is>
+      </c>
+      <c r="E810" s="5" t="inlineStr"/>
+      <c r="F810" s="5" t="inlineStr">
+        <is>
+          <t>إحالة نظامية</t>
+        </is>
+      </c>
+      <c r="G810" s="5" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H810" s="5" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="6" t="inlineStr">
+        <is>
+          <t>مستند_جديد_3_18121427.pdf</t>
+        </is>
+      </c>
+      <c r="B811" s="6" t="inlineStr">
+        <is>
+          <t>دليل/مستند</t>
+        </is>
+      </c>
+      <c r="C811" s="6" t="inlineStr">
+        <is>
+          <t>مستند، نسخة، بموجب</t>
+        </is>
+      </c>
+      <c r="D811" s="6" t="inlineStr">
+        <is>
+          <t>logical</t>
+        </is>
+      </c>
+      <c r="E811" s="6" t="inlineStr"/>
+      <c r="F811" s="6" t="inlineStr">
+        <is>
+          <t>دليل/مستند</t>
+        </is>
+      </c>
+      <c r="G811" s="6" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H811" s="6" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
